--- a/26-09_September_Metadata.xlsx
+++ b/26-09_September_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{48E6F19F-6C5F-40DD-8834-6B24BF9310B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2C88264-D494-4A9D-AA4F-604BB8955B6D}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{48E6F19F-6C5F-40DD-8834-6B24BF9310B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5D996F-2C13-4A34-935B-2C63707E0F76}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="411">
   <si>
     <t>Manuscript No.</t>
   </si>
@@ -1242,6 +1242,36 @@
   </si>
   <si>
     <t>833–847</t>
+  </si>
+  <si>
+    <t>SatSplat: Geometrically Accurate Gaussian Splatting for Satellite Imagery</t>
+  </si>
+  <si>
+    <t>High-speed videogrammetry, ellipse detection, circular marker, Sampson geometric error, weighted fusion, gray statistical constraint.</t>
+  </si>
+  <si>
+    <t>Circular marker detection plays an important role in high-speed videogrammetry applications, in which their accurate and reliable detection and localization is essential for precise motion measurement and deformation analysis. However, achieving high global detection accuracy with existing ellipse detection methods remains challenging in the presence of noise, background clutter or illumination variation, which often lead to missed detections and false positives. To address these challenges, this paper proposes a robust unsupervised ellipse detection method for circular markers, designed to minimize these errors and enhance detection accuracy. The proposed method comprises four components: initial ellipse set extraction, ellipse candidate generation, target ellipse detection, and target ellipse refinement. To improve detection performance, we introduce a reliable candidate generation approach coupled with a robust detection and refinement strategy. Experimental evaluation on multiple real-world data sets demonstrates that the proposed method outperforms reference methods, in particular in detection accuracy, while maintaining comparative computational efficiency.</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00020R3</t>
+  </si>
+  <si>
+    <t>1: School of Geography and Oceanography, Minjiang University 2: College of Surveying and Geoinformatics, Tongji University 3: Information Support Force Engineering University 4: College of Electronic Science, National University of Defense Technology 5: Institute of Cartography and Geographic Information System, Chinese Academy of Surveying and Mapping</t>
+  </si>
+  <si>
+    <t>Zheng, Shouzhu 1 ; Liu, Sicong 2 ; Song, Wenping 3, 4 ; Ye, Zhen 2 ; Ma, Xiaolong 5 ; Wang, Baohang 1 ; Zhang, Jianxia 1 ; </t>
+  </si>
+  <si>
+    <t>Robust Unsupervised Ellipse Detection for Circular Markers in High-Speed Videogrammetry</t>
+  </si>
+  <si>
+    <t>26-00020R3</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10JNDtebdPW2nfDXkgsX4rjhlYvoAeWc_/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14hZKvtY9FGnncxHBkUq2yHA7j7NRC_A4/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1472,28 +1502,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1517,6 +1529,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1836,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1897,279 +1913,279 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="29" customFormat="1" ht="150" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
+    <row r="2" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>46266</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="2">
         <v>92</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="2">
         <v>9</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="29" t="s">
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="2" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="29" customFormat="1" ht="240" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
+    <row r="3" spans="1:19" ht="240" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>46266</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="2">
         <v>92</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="2">
         <v>9</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="F3" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="29" t="s">
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J3" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="L3" s="29" t="s">
+      <c r="L3" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-    </row>
-    <row r="4" spans="1:19" s="29" customFormat="1" ht="180" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+    </row>
+    <row r="4" spans="1:19" ht="180" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>46266</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="2">
         <v>92</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="2">
         <v>9</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="29" t="s">
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="N4" s="2" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="29" customFormat="1" ht="195" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
+    <row r="5" spans="1:19" ht="195" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46266</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="2">
         <v>92</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="2">
         <v>9</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="29" t="s">
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="J5" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="L5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M5" s="29" t="s">
+      <c r="M5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="N5" s="29" t="s">
+      <c r="N5" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="O5" s="31"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="31"/>
-    </row>
-    <row r="6" spans="1:19" s="29" customFormat="1" ht="210" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="O5" s="4"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="4"/>
+    </row>
+    <row r="6" spans="1:19" ht="210" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>46266</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="2">
         <v>92</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="2">
         <v>9</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="29" t="s">
         <v>399</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="29" t="s">
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M6" s="29" t="s">
+      <c r="M6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="N6" s="29" t="s">
+      <c r="N6" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-    </row>
-    <row r="7" spans="1:19" s="29" customFormat="1" ht="210" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="P6" s="4"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+    </row>
+    <row r="7" spans="1:19" ht="210" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>46266</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="2">
         <v>92</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="2">
         <v>9</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="29" t="s">
+      <c r="F7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="2" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3512,6 +3528,9 @@
       <c r="G41" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="H41" s="2" t="s">
+        <v>401</v>
+      </c>
       <c r="I41" s="2" t="s">
         <v>326</v>
       </c>
@@ -3861,10 +3880,55 @@
       <c r="M49" s="2" t="s">
         <v>394</v>
       </c>
+      <c r="N49" s="2" t="s">
+        <v>410</v>
+      </c>
       <c r="O49" s="4"/>
       <c r="P49" s="23"/>
       <c r="Q49" s="20"/>
       <c r="R49" s="20"/>
+    </row>
+    <row r="50" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="O50" s="4"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="22"/>
+      <c r="R50" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:E12" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}"/>

--- a/26-09_September_Metadata.xlsx
+++ b/26-09_September_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{48E6F19F-6C5F-40DD-8834-6B24BF9310B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5D996F-2C13-4A34-935B-2C63707E0F76}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{48E6F19F-6C5F-40DD-8834-6B24BF9310B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F89D3E29-CFCC-483F-B19F-3B085EDBD8F8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="419">
   <si>
     <t>Manuscript No.</t>
   </si>
@@ -1272,6 +1272,30 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/14hZKvtY9FGnncxHBkUq2yHA7j7NRC_A4/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>China-Laos Railway, InSAR, Phase Gradient, Deformation Detection</t>
+  </si>
+  <si>
+    <t>The Kunming–Mohan section of the China–Laos Railway traverses complex mountainous terrain, making the rapid identification of deformation-prone areas essential for long-term operational safety. This study applied phase gradient stacking (PGS) to 200 wrapped differential interferograms generated under small-baseline criteria to detect deformation-gradient anomalies within a 10-km railway buffer. A normalized phase gradient index (PGI) was derived and jointly interpreted with time-series interferometric synthetic aperture radar (InSAR) displacements, digital elevation model–derived slope, and high-resolution optical imagery. The results show a low overall deformation-gradient intensity along the corridor, with a mean PGI of 0.08. Elevated PGI values are concentrated mainly in the central–northern corridor, particularly in Yuxi, which accounts for 54.9% of the strong-anomaly area. The PGS results are spatially consistent with time-series InSAR measurements in representative deformation zones. Infrastructure-scale analysis identified notable anomalies at Yanhe Station, the tunnel–bridge transition adjacent to the Babianjiang Bridge, and several tunnel portals. Multi-source interpretation further delineated 89 potentially unstable slopes, including 41 in Yuxi and 28 in Pu’er. Among them, 37 were attributed to natural slope evolution, while 26 were associated with engineering disturbance and 26 with reservoir infiltration. The results support PGS as an efficient, phase-unwrapping-free approach for first-pass screening of deformation-prone sections and prioritizing potentially unstable slopes along long mountainous railway corridors</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00085R2</t>
+  </si>
+  <si>
+    <t>1: School of Earth Sciences, Yunnan University 2: Yunnan International Joint Laboratory of China-Laos-Bangladesh-Myanmar Natural Resources Remote Sensing Monitoring 3: Yunnan Key Laboratory of Geohazard Forecast and Geoecological Restoration in Plateau Mountainous Area 4: Yunnan Institute of Geological Environment Monitoring</t>
+  </si>
+  <si>
+    <t>Yu, Yangwei 1 ; Zhao, Tianrui 1 ; Yang, Mengshi 1, 2 ; Yin, Kang 1 ; Huang, Weibin 1 ; Wu, Hao 1 ; Zhang, Yuhang 1 ; Huang, Cheng 3, 4 ; Zhao, Zhifang 1, 2 ; Xia, Jisheng 1, 2 ; </t>
+  </si>
+  <si>
+    <t>Rapid Detection of Deformation Anomalies along the China–Laos Railway Using InSAR Phase Gradient Stacking</t>
+  </si>
+  <si>
+    <t>26-00085R2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FHA5hDWj-Mdac2bACXsnbjJv-UkM-des/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -1852,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}">
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -3930,6 +3954,48 @@
       <c r="Q50" s="22"/>
       <c r="R50" s="21"/>
     </row>
+    <row r="51" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="O51" s="4"/>
+      <c r="P51" s="23"/>
+      <c r="Q51" s="20"/>
+      <c r="R51" s="20"/>
+    </row>
   </sheetData>
   <autoFilter ref="E1:E12" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}"/>
   <hyperlinks>
